--- a/kcylog/kcylog-ui/public/yszktj.xlsx
+++ b/kcylog/kcylog-ui/public/yszktj.xlsx
@@ -116,7 +116,7 @@
     <t>{totalOne}</t>
   </si>
   <si>
-    <t>{syclTow}</t>
+    <t>{syclTwo}</t>
   </si>
   <si>
     <t>{byxzTwo}</t>

--- a/kcylog/kcylog-ui/public/yszktj.xlsx
+++ b/kcylog/kcylog-ui/public/yszktj.xlsx
@@ -27,9 +27,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="42">
-  <si>
-    <t>应收账款月统计表（统计日期：{tjrq}） 单位（元）</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="59">
+  <si>
+    <t>应收账款月统计表（统计日期：{tjrq}） 单位（万元）</t>
   </si>
   <si>
     <t>部门名称</t>
@@ -153,6 +153,61 @@
   </si>
   <si>
     <t>应收款台账包含坏账台账</t>
+  </si>
+  <si>
+    <t>一年期内应收账款
+（万元）</t>
+  </si>
+  <si>
+    <t>一至三年之间应收账款
+（万元）</t>
+  </si>
+  <si>
+    <t>三年以上应收账款
+（万元）</t>
+  </si>
+  <si>
+    <t>合计
+（万元）</t>
+  </si>
+  <si>
+    <t>国有债权</t>
+  </si>
+  <si>
+    <t>民营债权</t>
+  </si>
+  <si>
+    <t>小计</t>
+  </si>
+  <si>
+    <t>{gyOne}</t>
+  </si>
+  <si>
+    <t>{myOne}</t>
+  </si>
+  <si>
+    <t>{gymyOne}</t>
+  </si>
+  <si>
+    <t>{gyTwo}</t>
+  </si>
+  <si>
+    <t>{myTwo}</t>
+  </si>
+  <si>
+    <t>{gymyTwo}</t>
+  </si>
+  <si>
+    <t>{gyThree}</t>
+  </si>
+  <si>
+    <t>{myThree}</t>
+  </si>
+  <si>
+    <t>{gymyThree}</t>
+  </si>
+  <si>
+    <t>{all}</t>
   </si>
 </sst>
 </file>
@@ -165,7 +220,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="28">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -196,6 +251,31 @@
     <font>
       <sz val="16"/>
       <color indexed="8"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color indexed="8"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="16"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -344,7 +424,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="39">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -365,6 +445,30 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799951170384838"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799951170384838"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEAD9FE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -550,7 +654,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="19">
     <border>
       <left/>
       <right/>
@@ -592,6 +696,89 @@
       <top style="thin">
         <color auto="1"/>
       </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
@@ -715,137 +902,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="11" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -876,11 +1063,74 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -888,7 +1138,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1416,8 +1666,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:U5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="4"/>
+  <dimension ref="A1:U11"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="2" width="19.875" style="1" customWidth="1"/>
     <col min="3" max="3" width="16.875" style="1" customWidth="1"/>
@@ -1428,8 +1678,7 @@
     <col min="8" max="8" width="16.9038461538462" style="1" customWidth="1"/>
     <col min="9" max="9" width="15.1442307692308" style="1" customWidth="1"/>
     <col min="10" max="10" width="18" style="1" customWidth="1"/>
-    <col min="11" max="11" width="16.9038461538462" style="1" customWidth="1"/>
-    <col min="12" max="12" width="18.875" style="1" customWidth="1"/>
+    <col min="11" max="12" width="18.875" style="1" customWidth="1"/>
     <col min="13" max="13" width="19.25" style="1" customWidth="1"/>
     <col min="14" max="14" width="19.0961538461538" style="1" customWidth="1"/>
     <col min="15" max="15" width="17.875" style="1" customWidth="1"/>
@@ -1555,7 +1804,7 @@
       <c r="T3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="U3" s="12" t="s">
+      <c r="U3" s="33" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1566,30 +1815,30 @@
       <c r="D4" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="10"/>
+      <c r="E4" s="20"/>
       <c r="F4" s="3"/>
       <c r="G4" s="3"/>
-      <c r="H4" s="14" t="s">
+      <c r="H4" s="35" t="s">
         <v>16</v>
       </c>
       <c r="I4" s="3"/>
-      <c r="J4" s="14" t="s">
+      <c r="J4" s="35" t="s">
         <v>17</v>
       </c>
       <c r="K4" s="3"/>
       <c r="L4" s="3"/>
       <c r="M4" s="3"/>
-      <c r="N4" s="14" t="s">
+      <c r="N4" s="35" t="s">
         <v>18</v>
       </c>
       <c r="O4" s="3"/>
-      <c r="P4" s="14" t="s">
+      <c r="P4" s="35" t="s">
         <v>19</v>
       </c>
       <c r="Q4" s="3"/>
       <c r="R4" s="3"/>
       <c r="S4" s="3"/>
-      <c r="T4" s="14" t="s">
+      <c r="T4" s="35" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1654,18 +1903,140 @@
       <c r="T5" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="U5" s="13" t="s">
+      <c r="U5" s="34" t="s">
         <v>41</v>
       </c>
+    </row>
+    <row r="8" ht="23.2" spans="1:13">
+      <c r="A8" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="B8" s="11"/>
+      <c r="C8" s="11"/>
+      <c r="D8" s="11"/>
+      <c r="E8" s="11"/>
+      <c r="F8" s="11"/>
+      <c r="G8" s="11"/>
+      <c r="H8" s="11"/>
+      <c r="I8" s="11"/>
+      <c r="J8" s="11"/>
+      <c r="K8" s="11"/>
+      <c r="L8" s="11"/>
+      <c r="M8" s="29"/>
+    </row>
+    <row r="9" ht="23.2" spans="1:13">
+      <c r="A9" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="B9" s="13"/>
+      <c r="C9" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="D9" s="15"/>
+      <c r="E9" s="22"/>
+      <c r="F9" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="G9" s="15"/>
+      <c r="H9" s="22"/>
+      <c r="I9" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="J9" s="15"/>
+      <c r="K9" s="22"/>
+      <c r="L9" s="25" t="s">
+        <v>45</v>
+      </c>
+      <c r="M9" s="30" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" ht="24" spans="1:13">
+      <c r="A10" s="16"/>
+      <c r="B10" s="17"/>
+      <c r="C10" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="D10" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="E10" s="23" t="s">
+        <v>48</v>
+      </c>
+      <c r="F10" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="G10" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="H10" s="24" t="s">
+        <v>48</v>
+      </c>
+      <c r="I10" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="J10" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="K10" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="L10" s="27"/>
+      <c r="M10" s="31"/>
+    </row>
+    <row r="11" ht="47" spans="1:13">
+      <c r="A11" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B11" s="17"/>
+      <c r="C11" s="19" t="s">
+        <v>49</v>
+      </c>
+      <c r="D11" s="18" t="s">
+        <v>50</v>
+      </c>
+      <c r="E11" s="23" t="s">
+        <v>51</v>
+      </c>
+      <c r="F11" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="G11" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="H11" s="23" t="s">
+        <v>54</v>
+      </c>
+      <c r="I11" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="J11" s="18" t="s">
+        <v>56</v>
+      </c>
+      <c r="K11" s="23" t="s">
+        <v>57</v>
+      </c>
+      <c r="L11" s="28" t="s">
+        <v>58</v>
+      </c>
+      <c r="M11" s="32"/>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="14">
     <mergeCell ref="A1:T1"/>
     <mergeCell ref="C2:H2"/>
     <mergeCell ref="I2:N2"/>
     <mergeCell ref="O2:T2"/>
+    <mergeCell ref="A8:M8"/>
+    <mergeCell ref="C9:E9"/>
+    <mergeCell ref="F9:H9"/>
+    <mergeCell ref="I9:K9"/>
+    <mergeCell ref="A11:B11"/>
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="B2:B3"/>
+    <mergeCell ref="L9:L10"/>
+    <mergeCell ref="M9:M10"/>
+    <mergeCell ref="A9:B10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/kcylog/kcylog-ui/public/yszktj.xlsx
+++ b/kcylog/kcylog-ui/public/yszktj.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="53">
   <si>
     <t>应收账款月统计表（统计日期：{tjrq}） 单位（万元）</t>
   </si>
@@ -72,24 +72,6 @@
   </si>
   <si>
     <t>备注</t>
-  </si>
-  <si>
-    <t>本月开票且回款的不统计</t>
-  </si>
-  <si>
-    <t>=上月存量+本月新增-本月回款-红冲（填写正数）-移至1到3年期</t>
-  </si>
-  <si>
-    <t>=移至1到3年期</t>
-  </si>
-  <si>
-    <t>=上月存量+本月新增-本月回款-红冲（填写正数）-移至3年期以上</t>
-  </si>
-  <si>
-    <t>=移至3年期以上</t>
-  </si>
-  <si>
-    <t>=上月存量+本月新增-本月回款-红冲（填写正数）-坏账处理</t>
   </si>
   <si>
     <t>福清分公司</t>
@@ -220,7 +202,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="28">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -247,25 +229,6 @@
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="16"/>
-      <color indexed="8"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="16"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="16"/>
-      <color indexed="8"/>
-      <name val="宋体"/>
-      <charset val="134"/>
     </font>
     <font>
       <b/>
@@ -424,7 +387,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="39">
+  <fills count="37">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -439,12 +402,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor indexed="13"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.799951170384838"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -542,12 +499,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -902,137 +853,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="11" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="11" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1051,94 +1002,70 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1666,7 +1593,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:U11"/>
+  <dimension ref="A1:U10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="2" width="19.875" style="1" customWidth="1"/>
@@ -1804,222 +1731,188 @@
       <c r="T3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="U3" s="33" t="s">
+      <c r="U3" s="26" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" ht="173.1" customHeight="1" spans="1:20">
-      <c r="A4" s="6"/>
-      <c r="B4" s="6"/>
-      <c r="C4" s="6"/>
+    <row r="4" s="2" customFormat="1" ht="47" spans="1:21">
+      <c r="A4" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="D4" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="E4" s="20"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
-      <c r="H4" s="35" t="s">
-        <v>16</v>
-      </c>
-      <c r="I4" s="3"/>
-      <c r="J4" s="35" t="s">
-        <v>17</v>
-      </c>
-      <c r="K4" s="3"/>
-      <c r="L4" s="3"/>
-      <c r="M4" s="3"/>
-      <c r="N4" s="35" t="s">
         <v>18</v>
       </c>
-      <c r="O4" s="3"/>
-      <c r="P4" s="35" t="s">
+      <c r="E4" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="Q4" s="3"/>
-      <c r="R4" s="3"/>
-      <c r="S4" s="3"/>
-      <c r="T4" s="35" t="s">
+      <c r="F4" s="7" t="s">
         <v>20</v>
       </c>
+      <c r="G4" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="H4" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J4" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="K4" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L4" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M4" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N4" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="O4" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="P4" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q4" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="R4" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="S4" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T4" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="U4" s="27" t="s">
+        <v>35</v>
+      </c>
     </row>
-    <row r="5" s="2" customFormat="1" ht="47" spans="1:21">
-      <c r="A5" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="D5" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="E5" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="F5" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G5" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="H5" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="J5" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="K5" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="L5" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="M5" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="N5" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="O5" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="P5" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="Q5" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="R5" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="S5" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="T5" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="U5" s="34" t="s">
-        <v>41</v>
-      </c>
+    <row r="7" ht="23.2" spans="1:13">
+      <c r="A7" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="4"/>
+      <c r="J7" s="4"/>
+      <c r="K7" s="4"/>
+      <c r="L7" s="4"/>
+      <c r="M7" s="5"/>
     </row>
     <row r="8" ht="23.2" spans="1:13">
-      <c r="A8" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="B8" s="11"/>
-      <c r="C8" s="11"/>
-      <c r="D8" s="11"/>
-      <c r="E8" s="11"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="11"/>
-      <c r="H8" s="11"/>
-      <c r="I8" s="11"/>
-      <c r="J8" s="11"/>
-      <c r="K8" s="11"/>
-      <c r="L8" s="11"/>
-      <c r="M8" s="29"/>
+      <c r="A8" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8" s="10"/>
+      <c r="C8" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="D8" s="12"/>
+      <c r="E8" s="16"/>
+      <c r="F8" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="G8" s="12"/>
+      <c r="H8" s="16"/>
+      <c r="I8" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="J8" s="12"/>
+      <c r="K8" s="16"/>
+      <c r="L8" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="M8" s="23" t="s">
+        <v>14</v>
+      </c>
     </row>
-    <row r="9" ht="23.2" spans="1:13">
-      <c r="A9" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="B9" s="13"/>
-      <c r="C9" s="14" t="s">
+    <row r="9" ht="24" spans="1:13">
+      <c r="A9" s="13"/>
+      <c r="B9" s="14"/>
+      <c r="C9" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="E9" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="D9" s="15"/>
-      <c r="E9" s="22"/>
-      <c r="F9" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="G9" s="15"/>
-      <c r="H9" s="22"/>
-      <c r="I9" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="J9" s="15"/>
-      <c r="K9" s="22"/>
-      <c r="L9" s="25" t="s">
-        <v>45</v>
-      </c>
-      <c r="M9" s="30" t="s">
-        <v>14</v>
-      </c>
+      <c r="F9" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="H9" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="I9" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="J9" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="K9" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="L9" s="21"/>
+      <c r="M9" s="24"/>
     </row>
     <row r="10" ht="24" spans="1:13">
-      <c r="A10" s="16"/>
-      <c r="B10" s="17"/>
-      <c r="C10" s="18" t="s">
+      <c r="A10" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" s="14"/>
+      <c r="C10" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="E10" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="F10" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="D10" s="18" t="s">
+      <c r="G10" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="E10" s="23" t="s">
+      <c r="H10" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="F10" s="18" t="s">
-        <v>46</v>
-      </c>
-      <c r="G10" s="18" t="s">
-        <v>47</v>
-      </c>
-      <c r="H10" s="24" t="s">
-        <v>48</v>
-      </c>
-      <c r="I10" s="18" t="s">
-        <v>46</v>
-      </c>
-      <c r="J10" s="18" t="s">
-        <v>47</v>
-      </c>
-      <c r="K10" s="26" t="s">
-        <v>48</v>
-      </c>
-      <c r="L10" s="27"/>
-      <c r="M10" s="31"/>
-    </row>
-    <row r="11" ht="47" spans="1:13">
-      <c r="A11" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="B11" s="17"/>
-      <c r="C11" s="19" t="s">
+      <c r="I10" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="D11" s="18" t="s">
+      <c r="J10" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="E11" s="23" t="s">
+      <c r="K10" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="F11" s="19" t="s">
+      <c r="L10" s="22" t="s">
         <v>52</v>
       </c>
-      <c r="G11" s="18" t="s">
-        <v>53</v>
-      </c>
-      <c r="H11" s="23" t="s">
-        <v>54</v>
-      </c>
-      <c r="I11" s="19" t="s">
-        <v>55</v>
-      </c>
-      <c r="J11" s="18" t="s">
-        <v>56</v>
-      </c>
-      <c r="K11" s="23" t="s">
-        <v>57</v>
-      </c>
-      <c r="L11" s="28" t="s">
-        <v>58</v>
-      </c>
-      <c r="M11" s="32"/>
+      <c r="M10" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="14">
@@ -2027,16 +1920,16 @@
     <mergeCell ref="C2:H2"/>
     <mergeCell ref="I2:N2"/>
     <mergeCell ref="O2:T2"/>
-    <mergeCell ref="A8:M8"/>
-    <mergeCell ref="C9:E9"/>
-    <mergeCell ref="F9:H9"/>
-    <mergeCell ref="I9:K9"/>
-    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A7:M7"/>
+    <mergeCell ref="C8:E8"/>
+    <mergeCell ref="F8:H8"/>
+    <mergeCell ref="I8:K8"/>
+    <mergeCell ref="A10:B10"/>
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="B2:B3"/>
-    <mergeCell ref="L9:L10"/>
-    <mergeCell ref="M9:M10"/>
-    <mergeCell ref="A9:B10"/>
+    <mergeCell ref="L8:L9"/>
+    <mergeCell ref="M8:M9"/>
+    <mergeCell ref="A8:B9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/kcylog/kcylog-ui/public/yszktj.xlsx
+++ b/kcylog/kcylog-ui/public/yszktj.xlsx
@@ -414,13 +414,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFEAD9FE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -928,7 +928,7 @@
     <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1005,33 +1005,33 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1041,23 +1041,23 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1593,36 +1593,35 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:U10"/>
+  <dimension ref="B1:V10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
-    <col min="1" max="2" width="19.875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="16.875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="15.625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="16.4615384615385" style="1" customWidth="1"/>
-    <col min="6" max="6" width="19.625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="18.125" style="1" customWidth="1"/>
-    <col min="8" max="8" width="16.9038461538462" style="1" customWidth="1"/>
-    <col min="9" max="9" width="15.1442307692308" style="1" customWidth="1"/>
-    <col min="10" max="10" width="18" style="1" customWidth="1"/>
-    <col min="11" max="12" width="18.875" style="1" customWidth="1"/>
-    <col min="13" max="13" width="19.25" style="1" customWidth="1"/>
-    <col min="14" max="14" width="19.0961538461538" style="1" customWidth="1"/>
-    <col min="15" max="15" width="17.875" style="1" customWidth="1"/>
-    <col min="16" max="16" width="17.5576923076923" style="1" customWidth="1"/>
-    <col min="17" max="17" width="17.5480769230769" style="1" customWidth="1"/>
-    <col min="18" max="18" width="21.875" style="1" customWidth="1"/>
-    <col min="19" max="19" width="15.625" style="1" customWidth="1"/>
-    <col min="20" max="20" width="18.6538461538462" style="1" customWidth="1"/>
-    <col min="21" max="21" width="20.875" style="1" customWidth="1"/>
-    <col min="22" max="16383" width="9" style="1"/>
+    <col min="2" max="3" width="19.875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="16.875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="15.625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="16.4615384615385" style="1" customWidth="1"/>
+    <col min="7" max="7" width="19.625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="18.125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="16.9038461538462" style="1" customWidth="1"/>
+    <col min="10" max="10" width="15.1442307692308" style="1" customWidth="1"/>
+    <col min="11" max="11" width="18" style="1" customWidth="1"/>
+    <col min="12" max="13" width="18.875" style="1" customWidth="1"/>
+    <col min="14" max="14" width="19.25" style="1" customWidth="1"/>
+    <col min="15" max="15" width="19.0961538461538" style="1" customWidth="1"/>
+    <col min="16" max="16" width="17.875" style="1" customWidth="1"/>
+    <col min="17" max="17" width="17.5576923076923" style="1" customWidth="1"/>
+    <col min="18" max="18" width="17.5480769230769" style="1" customWidth="1"/>
+    <col min="19" max="19" width="21.875" style="1" customWidth="1"/>
+    <col min="20" max="20" width="15.625" style="1" customWidth="1"/>
+    <col min="21" max="21" width="18.6538461538462" style="1" customWidth="1"/>
+    <col min="22" max="22" width="20.875" style="1" customWidth="1"/>
+    <col min="23" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="30.95" customHeight="1" spans="1:20">
-      <c r="A1" s="3" t="s">
+    <row r="1" s="1" customFormat="1" ht="30.95" customHeight="1" spans="2:21">
+      <c r="B1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3"/>
       <c r="C1" s="3"/>
       <c r="D1" s="3"/>
       <c r="E1" s="3"/>
@@ -1641,170 +1640,170 @@
       <c r="R1" s="3"/>
       <c r="S1" s="3"/>
       <c r="T1" s="3"/>
+      <c r="U1" s="3"/>
     </row>
-    <row r="2" s="1" customFormat="1" ht="39.95" customHeight="1" spans="1:20">
-      <c r="A2" s="3" t="s">
+    <row r="2" s="1" customFormat="1" ht="39.95" customHeight="1" spans="2:21">
+      <c r="B2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="C2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="D2" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="4"/>
       <c r="E2" s="4"/>
       <c r="F2" s="4"/>
       <c r="G2" s="4"/>
-      <c r="H2" s="5"/>
-      <c r="I2" s="3" t="s">
+      <c r="H2" s="4"/>
+      <c r="I2" s="5"/>
+      <c r="J2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J2" s="3"/>
       <c r="K2" s="3"/>
       <c r="L2" s="3"/>
       <c r="M2" s="3"/>
       <c r="N2" s="3"/>
-      <c r="O2" s="3" t="s">
+      <c r="O2" s="3"/>
+      <c r="P2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P2" s="3"/>
       <c r="Q2" s="3"/>
       <c r="R2" s="3"/>
       <c r="S2" s="3"/>
       <c r="T2" s="3"/>
+      <c r="U2" s="3"/>
     </row>
-    <row r="3" s="1" customFormat="1" ht="77.1" customHeight="1" spans="1:21">
-      <c r="A3" s="3"/>
+    <row r="3" s="1" customFormat="1" ht="77.1" customHeight="1" spans="2:22">
       <c r="B3" s="3"/>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="3"/>
+      <c r="D3" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="E3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="F3" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="G3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="H3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="I3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="J3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="K3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="K3" s="3" t="s">
+      <c r="L3" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L3" s="3" t="s">
+      <c r="M3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="M3" s="3" t="s">
+      <c r="N3" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="N3" s="3" t="s">
+      <c r="O3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="O3" s="3" t="s">
+      <c r="P3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="P3" s="3" t="s">
+      <c r="Q3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="Q3" s="3" t="s">
+      <c r="R3" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R3" s="3" t="s">
+      <c r="S3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="S3" s="3" t="s">
+      <c r="T3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="T3" s="3" t="s">
+      <c r="U3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="U3" s="26" t="s">
+      <c r="V3" s="26" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="4" s="2" customFormat="1" ht="47" spans="1:21">
-      <c r="A4" s="6" t="s">
+    <row r="4" s="2" customFormat="1" ht="47" spans="2:22">
+      <c r="B4" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="C4" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="D4" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="E4" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="F4" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="G4" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="G4" s="7" t="s">
+      <c r="H4" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="H4" s="7" t="s">
+      <c r="I4" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="J4" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="J4" s="7" t="s">
+      <c r="K4" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="K4" s="7" t="s">
+      <c r="L4" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="L4" s="7" t="s">
+      <c r="M4" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="M4" s="7" t="s">
+      <c r="N4" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="N4" s="7" t="s">
+      <c r="O4" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="O4" s="3" t="s">
+      <c r="P4" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="P4" s="7" t="s">
+      <c r="Q4" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="Q4" s="7" t="s">
+      <c r="R4" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="R4" s="7" t="s">
+      <c r="S4" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="S4" s="7" t="s">
+      <c r="T4" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="T4" s="7" t="s">
+      <c r="U4" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="U4" s="27" t="s">
+      <c r="V4" s="27" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="7" ht="23.2" spans="1:13">
-      <c r="A7" s="8" t="s">
+    <row r="7" ht="23.2" spans="2:14">
+      <c r="B7" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B7" s="4"/>
       <c r="C7" s="4"/>
       <c r="D7" s="4"/>
       <c r="E7" s="4"/>
@@ -1815,121 +1814,122 @@
       <c r="J7" s="4"/>
       <c r="K7" s="4"/>
       <c r="L7" s="4"/>
-      <c r="M7" s="5"/>
+      <c r="M7" s="4"/>
+      <c r="N7" s="5"/>
     </row>
-    <row r="8" ht="23.2" spans="1:13">
-      <c r="A8" s="9" t="s">
+    <row r="8" ht="23.2" spans="2:14">
+      <c r="B8" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="10"/>
-      <c r="C8" s="11" t="s">
+      <c r="C8" s="9"/>
+      <c r="D8" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="D8" s="12"/>
-      <c r="E8" s="16"/>
-      <c r="F8" s="11" t="s">
+      <c r="E8" s="15"/>
+      <c r="F8" s="16"/>
+      <c r="G8" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="G8" s="12"/>
-      <c r="H8" s="16"/>
-      <c r="I8" s="11" t="s">
+      <c r="H8" s="15"/>
+      <c r="I8" s="16"/>
+      <c r="J8" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="J8" s="12"/>
-      <c r="K8" s="16"/>
-      <c r="L8" s="19" t="s">
+      <c r="K8" s="15"/>
+      <c r="L8" s="16"/>
+      <c r="M8" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="M8" s="23" t="s">
+      <c r="N8" s="21" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="9" ht="24" spans="1:13">
-      <c r="A9" s="13"/>
-      <c r="B9" s="14"/>
-      <c r="C9" s="6" t="s">
+    <row r="9" ht="24" spans="2:14">
+      <c r="B9" s="11"/>
+      <c r="C9" s="12"/>
+      <c r="D9" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="E9" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="E9" s="17" t="s">
+      <c r="F9" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="F9" s="6" t="s">
+      <c r="G9" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="G9" s="6" t="s">
+      <c r="H9" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="H9" s="18" t="s">
+      <c r="I9" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="I9" s="6" t="s">
+      <c r="J9" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="J9" s="6" t="s">
+      <c r="K9" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="K9" s="20" t="s">
+      <c r="L9" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="L9" s="21"/>
-      <c r="M9" s="24"/>
+      <c r="M9" s="22"/>
+      <c r="N9" s="23"/>
     </row>
-    <row r="10" ht="24" spans="1:13">
-      <c r="A10" s="13" t="s">
+    <row r="10" ht="24" spans="2:14">
+      <c r="B10" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="B10" s="14"/>
-      <c r="C10" s="15" t="s">
+      <c r="C10" s="12"/>
+      <c r="D10" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="D10" s="6" t="s">
+      <c r="E10" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="E10" s="17" t="s">
+      <c r="F10" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="F10" s="15" t="s">
+      <c r="G10" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="G10" s="6" t="s">
+      <c r="H10" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="H10" s="17" t="s">
+      <c r="I10" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="I10" s="15" t="s">
+      <c r="J10" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="J10" s="6" t="s">
+      <c r="K10" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="K10" s="17" t="s">
+      <c r="L10" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="L10" s="22" t="s">
+      <c r="M10" s="24" t="s">
         <v>52</v>
       </c>
-      <c r="M10" s="25"/>
+      <c r="N10" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="A1:T1"/>
-    <mergeCell ref="C2:H2"/>
-    <mergeCell ref="I2:N2"/>
-    <mergeCell ref="O2:T2"/>
-    <mergeCell ref="A7:M7"/>
-    <mergeCell ref="C8:E8"/>
-    <mergeCell ref="F8:H8"/>
-    <mergeCell ref="I8:K8"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="B1:U1"/>
+    <mergeCell ref="D2:I2"/>
+    <mergeCell ref="J2:O2"/>
+    <mergeCell ref="P2:U2"/>
+    <mergeCell ref="B7:N7"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="J8:L8"/>
+    <mergeCell ref="B10:C10"/>
     <mergeCell ref="B2:B3"/>
-    <mergeCell ref="L8:L9"/>
+    <mergeCell ref="C2:C3"/>
     <mergeCell ref="M8:M9"/>
-    <mergeCell ref="A8:B9"/>
+    <mergeCell ref="N8:N9"/>
+    <mergeCell ref="B8:C9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/kcylog/kcylog-ui/public/yszktj.xlsx
+++ b/kcylog/kcylog-ui/public/yszktj.xlsx
@@ -387,18 +387,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="37">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -859,7 +853,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="11" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="11" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -883,16 +877,16 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -901,89 +895,89 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1023,41 +1017,32 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1731,7 +1716,7 @@
       <c r="U3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="V3" s="26" t="s">
+      <c r="V3" s="23" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1742,61 +1727,61 @@
       <c r="C4" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="E4" s="14" t="s">
+      <c r="E4" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="F4" s="14" t="s">
+      <c r="F4" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="G4" s="14" t="s">
+      <c r="G4" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="H4" s="14" t="s">
+      <c r="H4" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="I4" s="14" t="s">
+      <c r="I4" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="J4" s="3" t="s">
+      <c r="J4" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="K4" s="14" t="s">
+      <c r="K4" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="L4" s="14" t="s">
+      <c r="L4" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="M4" s="14" t="s">
+      <c r="M4" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="N4" s="14" t="s">
+      <c r="N4" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="O4" s="14" t="s">
+      <c r="O4" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="P4" s="3" t="s">
+      <c r="P4" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="Q4" s="14" t="s">
+      <c r="Q4" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="R4" s="14" t="s">
+      <c r="R4" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="S4" s="14" t="s">
+      <c r="S4" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="T4" s="14" t="s">
+      <c r="T4" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="U4" s="14" t="s">
+      <c r="U4" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="V4" s="27" t="s">
+      <c r="V4" s="24" t="s">
         <v>35</v>
       </c>
     </row>
@@ -1825,22 +1810,22 @@
       <c r="D8" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="E8" s="15"/>
-      <c r="F8" s="16"/>
+      <c r="E8" s="13"/>
+      <c r="F8" s="14"/>
       <c r="G8" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="H8" s="15"/>
-      <c r="I8" s="16"/>
+      <c r="H8" s="13"/>
+      <c r="I8" s="14"/>
       <c r="J8" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="K8" s="15"/>
-      <c r="L8" s="16"/>
-      <c r="M8" s="20" t="s">
+      <c r="K8" s="13"/>
+      <c r="L8" s="14"/>
+      <c r="M8" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="N8" s="21" t="s">
+      <c r="N8" s="19" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1853,7 +1838,7 @@
       <c r="E9" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="F9" s="17" t="s">
+      <c r="F9" s="15" t="s">
         <v>42</v>
       </c>
       <c r="G9" s="6" t="s">
@@ -1862,7 +1847,7 @@
       <c r="H9" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="I9" s="18" t="s">
+      <c r="I9" s="16" t="s">
         <v>42</v>
       </c>
       <c r="J9" s="6" t="s">
@@ -1871,48 +1856,48 @@
       <c r="K9" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="L9" s="19" t="s">
+      <c r="L9" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="M9" s="22"/>
-      <c r="N9" s="23"/>
+      <c r="M9" s="20"/>
+      <c r="N9" s="21"/>
     </row>
     <row r="10" ht="24" spans="2:14">
       <c r="B10" s="11" t="s">
         <v>15</v>
       </c>
       <c r="C10" s="12"/>
-      <c r="D10" s="13" t="s">
+      <c r="D10" s="6" t="s">
         <v>43</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="F10" s="17" t="s">
+      <c r="F10" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="G10" s="13" t="s">
+      <c r="G10" s="6" t="s">
         <v>46</v>
       </c>
       <c r="H10" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="I10" s="17" t="s">
+      <c r="I10" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="J10" s="13" t="s">
+      <c r="J10" s="6" t="s">
         <v>49</v>
       </c>
       <c r="K10" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="L10" s="17" t="s">
+      <c r="L10" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="M10" s="24" t="s">
+      <c r="M10" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="N10" s="25"/>
+      <c r="N10" s="22"/>
     </row>
   </sheetData>
   <mergeCells count="14">
